--- a/examples/LLC_Accounting_Template.xlsx
+++ b/examples/LLC_Accounting_Template.xlsx
@@ -42,7 +42,7 @@
     <t>Sheet Name (Config)</t>
   </si>
   <si>
-    <t>Account Type</t>
+    <t>Sheet Type</t>
   </si>
   <si>
     <t>Flip Polarity? (Yes/No)</t>
@@ -66,54 +66,54 @@
     <t>Starbucks</t>
   </si>
   <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>Expense</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Checking Account</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Asset</t>
+  </si>
+  <si>
+    <t>Balance Sheet</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
     <t>Bank Transactions</t>
   </si>
   <si>
-    <t>Bank</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Rent</t>
-  </si>
-  <si>
-    <t>Office</t>
-  </si>
-  <si>
-    <t>Expense</t>
-  </si>
-  <si>
-    <t>Amazon</t>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Liability</t>
   </si>
   <si>
     <t>Credit Card Transactions</t>
   </si>
   <si>
-    <t>CC</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Checking Account</t>
-  </si>
-  <si>
-    <t>Asset</t>
-  </si>
-  <si>
-    <t>Balance Sheet</t>
-  </si>
-  <si>
-    <t>AWS</t>
-  </si>
-  <si>
-    <t>Credit Card</t>
-  </si>
-  <si>
-    <t>Liability</t>
-  </si>
-  <si>
     <t>AX CC</t>
   </si>
   <si>
@@ -162,19 +162,19 @@
     <t>Version ID</t>
   </si>
   <si>
-    <t>1.0.0-java</t>
+    <t>3.0.142</t>
   </si>
   <si>
     <t>Git SHA</t>
   </si>
   <si>
-    <t>fa8999fc0a5c37c5e114a44cb01475b5da278394</t>
+    <t>d307335a4428c01d3d82d91d7307ace54f8c30ce</t>
   </si>
   <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>12/22/2025, 10:07:03 AM</t>
+    <t>9/25/2026, 8:22:01 PM</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -619,77 +619,77 @@
       <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="K2" t="s">
+      <c r="C3" t="s">
         <v>18</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="F3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="s">
+      <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="J3" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="K3" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="L4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
+      <c r="L5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -697,13 +697,13 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/examples/LLC_Accounting_Template.xlsx
+++ b/examples/LLC_Accounting_Template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="54">
   <si>
     <t>Category</t>
   </si>
@@ -51,6 +51,9 @@
     <t>Header Row</t>
   </si>
   <si>
+    <t>End Balance</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
@@ -168,13 +171,13 @@
     <t>Git SHA</t>
   </si>
   <si>
-    <t>d307335a4428c01d3d82d91d7307ace54f8c30ce</t>
+    <t>08f61282a92ff4007f08418c5e623f1acc0b7708</t>
   </si>
   <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>9/25/2026, 8:22:01 PM</t>
+    <t>10/29/2026, 8:59:57 AM</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -562,10 +565,10 @@
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="12" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -602,108 +605,117 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5">
         <v>3</v>
       </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -728,13 +740,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -743,16 +755,16 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -781,16 +793,16 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -799,22 +811,22 @@
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -837,22 +849,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -882,34 +894,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
